--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,8 +774,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98308452</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,9 +780,3240 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135619959</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>353</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>679812</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7321979</v>
+      </c>
+      <c r="S3" t="n">
+        <v>27</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619959</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135619965</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>679806</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7322095</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619965</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135619977</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>679670</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7322193</v>
+      </c>
+      <c r="S5" t="n">
+        <v>69</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619977</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135619979</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92153</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>679635</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7322208</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619979</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135619967</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>679755</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7322069</v>
+      </c>
+      <c r="S7" t="n">
+        <v>17</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619967</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135619978</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>679637</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7322205</v>
+      </c>
+      <c r="S8" t="n">
+        <v>43</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619978</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135619962</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>679861</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7321962</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619962</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135619971</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>679746</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7322048</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619971</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135619976</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>679673</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7322179</v>
+      </c>
+      <c r="S11" t="n">
+        <v>68</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619976</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135619952</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>679574</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7321815</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619952</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135619958</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>679814</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7321960</v>
+      </c>
+      <c r="S13" t="n">
+        <v>96</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619958</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135619969</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>679744</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7322052</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619969</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135619981</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>679630</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7322240</v>
+      </c>
+      <c r="S15" t="n">
+        <v>22</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619981</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135619972</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>679746</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7322048</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619972</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135619975</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>679673</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7322179</v>
+      </c>
+      <c r="S17" t="n">
+        <v>64</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619975</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135619953</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>679642</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7321835</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619953</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135619957</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>679790</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7321957</v>
+      </c>
+      <c r="S19" t="n">
+        <v>16</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619957</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135619963</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>679845</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7322112</v>
+      </c>
+      <c r="S20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619963</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135619964</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>679863</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7322052</v>
+      </c>
+      <c r="S21" t="n">
+        <v>22</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619964</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135619966</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>679785</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7322100</v>
+      </c>
+      <c r="S22" t="n">
+        <v>44</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619966</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135619982</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>679625</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7322249</v>
+      </c>
+      <c r="S23" t="n">
+        <v>41</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619982</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135619973</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>679752</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7322097</v>
+      </c>
+      <c r="S24" t="n">
+        <v>48</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619973</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135619960</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>679846</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7321962</v>
+      </c>
+      <c r="S25" t="n">
+        <v>21</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619960</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135619970</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>679752</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7322054</v>
+      </c>
+      <c r="S26" t="n">
+        <v>14</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619970</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135619974</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>679682</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7322160</v>
+      </c>
+      <c r="S27" t="n">
+        <v>7</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619974</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135619961</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>679862</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7321960</v>
+      </c>
+      <c r="S28" t="n">
+        <v>11</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619961</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135619954</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80267</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>679703</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7321883</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619954</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135619980</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80267</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>679628</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7322239</v>
+      </c>
+      <c r="S30" t="n">
+        <v>33</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619980</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,7 +785,7 @@
         <v>135619959</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135619965</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135619977</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135619979</v>
       </c>
       <c r="B6" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135619967</v>
+        <v>135637876</v>
       </c>
       <c r="B7" t="n">
-        <v>92027</v>
+        <v>91039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,37 +1241,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679755</v>
+        <v>679750</v>
       </c>
       <c r="R7" t="n">
-        <v>7322069</v>
+        <v>7321882</v>
       </c>
       <c r="S7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,27 +1325,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619967</t>
+          <t>https://artportalen.se/Sighting/135637876</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135619978</v>
+        <v>135637880</v>
       </c>
       <c r="B8" t="n">
-        <v>92027</v>
+        <v>91039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,37 +1353,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679637</v>
+        <v>679870</v>
       </c>
       <c r="R8" t="n">
-        <v>7322205</v>
+        <v>7322041</v>
       </c>
       <c r="S8" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,49 +1437,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619978</t>
+          <t>https://artportalen.se/Sighting/135637880</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135619962</v>
+        <v>135619967</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>92069</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,13 +1489,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679861</v>
+        <v>679755</v>
       </c>
       <c r="R9" t="n">
-        <v>7321962</v>
+        <v>7322069</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,16 +1560,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619962</t>
+          <t>https://artportalen.se/Sighting/135619967</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135619971</v>
+        <v>135619978</v>
       </c>
       <c r="B10" t="n">
-        <v>78776</v>
+        <v>92069</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>679746</v>
+        <v>679637</v>
       </c>
       <c r="R10" t="n">
-        <v>7322048</v>
+        <v>7322205</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,16 +1672,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619971</t>
+          <t>https://artportalen.se/Sighting/135619978</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135619976</v>
+        <v>135637882</v>
       </c>
       <c r="B11" t="n">
-        <v>78776</v>
+        <v>92069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,37 +1689,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679673</v>
+        <v>679833</v>
       </c>
       <c r="R11" t="n">
-        <v>7322179</v>
+        <v>7322085</v>
       </c>
       <c r="S11" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,55 +1767,56 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619976</t>
+          <t>https://artportalen.se/Sighting/135637882</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135619952</v>
+        <v>135619962</v>
       </c>
       <c r="B12" t="n">
-        <v>79992</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,13 +1826,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679574</v>
+        <v>679861</v>
       </c>
       <c r="R12" t="n">
-        <v>7321815</v>
+        <v>7321962</v>
       </c>
       <c r="S12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,16 +1897,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619952</t>
+          <t>https://artportalen.se/Sighting/135619962</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135619958</v>
+        <v>135619971</v>
       </c>
       <c r="B13" t="n">
-        <v>79992</v>
+        <v>78814</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,21 +1914,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1938,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679814</v>
+        <v>679746</v>
       </c>
       <c r="R13" t="n">
-        <v>7321960</v>
+        <v>7322048</v>
       </c>
       <c r="S13" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1973,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1983,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,16 +2009,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619958</t>
+          <t>https://artportalen.se/Sighting/135619971</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135619969</v>
+        <v>135619976</v>
       </c>
       <c r="B14" t="n">
-        <v>79992</v>
+        <v>78814</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,21 +2026,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,13 +2050,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679744</v>
+        <v>679673</v>
       </c>
       <c r="R14" t="n">
-        <v>7322052</v>
+        <v>7322179</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2085,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2095,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,16 +2121,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619969</t>
+          <t>https://artportalen.se/Sighting/135619976</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135619981</v>
+        <v>135637877</v>
       </c>
       <c r="B15" t="n">
-        <v>79992</v>
+        <v>78814</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,37 +2138,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679630</v>
+        <v>679736</v>
       </c>
       <c r="R15" t="n">
-        <v>7322240</v>
+        <v>7321943</v>
       </c>
       <c r="S15" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2196,7 +2197,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2207,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,27 +2222,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619981</t>
+          <t>https://artportalen.se/Sighting/135637877</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135619972</v>
+        <v>135619952</v>
       </c>
       <c r="B16" t="n">
-        <v>78377</v>
+        <v>80030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,21 +2250,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,13 +2274,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679746</v>
+        <v>679574</v>
       </c>
       <c r="R16" t="n">
-        <v>7322048</v>
+        <v>7321815</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2308,7 +2309,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2318,7 +2319,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,16 +2345,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619972</t>
+          <t>https://artportalen.se/Sighting/135619952</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135619975</v>
+        <v>135619958</v>
       </c>
       <c r="B17" t="n">
-        <v>78377</v>
+        <v>80030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,21 +2362,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,13 +2386,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>679673</v>
+        <v>679814</v>
       </c>
       <c r="R17" t="n">
-        <v>7322179</v>
+        <v>7321960</v>
       </c>
       <c r="S17" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2420,7 +2421,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2430,7 +2431,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2456,16 +2457,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619975</t>
+          <t>https://artportalen.se/Sighting/135619958</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135619953</v>
+        <v>135619969</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>80030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,42 +2474,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679642</v>
+        <v>679744</v>
       </c>
       <c r="R18" t="n">
-        <v>7321835</v>
+        <v>7322052</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2537,7 +2533,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2547,12 +2543,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2578,16 +2569,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619953</t>
+          <t>https://artportalen.se/Sighting/135619969</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135619957</v>
+        <v>135619981</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>80030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,45 +2586,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679790</v>
+        <v>679630</v>
       </c>
       <c r="R19" t="n">
-        <v>7321957</v>
+        <v>7322240</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2662,7 +2645,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2672,19 +2655,14 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2703,16 +2681,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619957</t>
+          <t>https://artportalen.se/Sighting/135619981</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135619963</v>
+        <v>135637870</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>80030</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2720,45 +2698,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679845</v>
+        <v>679550</v>
       </c>
       <c r="R20" t="n">
-        <v>7322112</v>
+        <v>7321796</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2787,7 +2757,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2797,19 +2767,14 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2817,27 +2782,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619963</t>
+          <t>https://artportalen.se/Sighting/135637870</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135619964</v>
+        <v>135619972</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>78415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,42 +2810,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679863</v>
+        <v>679746</v>
       </c>
       <c r="R21" t="n">
-        <v>7322052</v>
+        <v>7322048</v>
       </c>
       <c r="S21" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2909,7 +2869,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2919,12 +2879,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2950,16 +2905,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619964</t>
+          <t>https://artportalen.se/Sighting/135619972</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135619966</v>
+        <v>135619975</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>78415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2967,45 +2922,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>679785</v>
+        <v>679673</v>
       </c>
       <c r="R22" t="n">
-        <v>7322100</v>
+        <v>7322179</v>
       </c>
       <c r="S22" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3034,7 +2981,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3044,19 +2991,14 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -3075,16 +3017,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619966</t>
+          <t>https://artportalen.se/Sighting/135619975</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135619982</v>
+        <v>135619953</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,27 +3052,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679625</v>
+        <v>679642</v>
       </c>
       <c r="R23" t="n">
-        <v>7322249</v>
+        <v>7321835</v>
       </c>
       <c r="S23" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3159,7 +3098,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,19 +3108,19 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hackmärken från födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3200,16 +3139,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619982</t>
+          <t>https://artportalen.se/Sighting/135619953</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135619973</v>
+        <v>135619957</v>
       </c>
       <c r="B24" t="n">
-        <v>58136</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3217,37 +3156,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679752</v>
+        <v>679790</v>
       </c>
       <c r="R24" t="n">
-        <v>7322097</v>
+        <v>7321957</v>
       </c>
       <c r="S24" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3276,7 +3223,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3286,14 +3233,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3312,16 +3264,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619973</t>
+          <t>https://artportalen.se/Sighting/135619957</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135619960</v>
+        <v>135619963</v>
       </c>
       <c r="B25" t="n">
-        <v>58079</v>
+        <v>57980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3329,16 +3281,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3347,24 +3299,27 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679846</v>
+        <v>679845</v>
       </c>
       <c r="R25" t="n">
-        <v>7321962</v>
+        <v>7322112</v>
       </c>
       <c r="S25" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3393,7 +3348,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3403,14 +3358,19 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3429,16 +3389,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619960</t>
+          <t>https://artportalen.se/Sighting/135619963</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135619970</v>
+        <v>135619964</v>
       </c>
       <c r="B26" t="n">
-        <v>79963</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,37 +3406,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679752</v>
+        <v>679863</v>
       </c>
       <c r="R26" t="n">
-        <v>7322054</v>
+        <v>7322052</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3505,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3515,7 +3480,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3541,16 +3511,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619970</t>
+          <t>https://artportalen.se/Sighting/135619964</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135619974</v>
+        <v>135619966</v>
       </c>
       <c r="B27" t="n">
-        <v>79963</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3558,37 +3528,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679682</v>
+        <v>679785</v>
       </c>
       <c r="R27" t="n">
-        <v>7322160</v>
+        <v>7322100</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3617,7 +3595,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3627,14 +3605,19 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3653,16 +3636,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619974</t>
+          <t>https://artportalen.se/Sighting/135619966</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135619961</v>
+        <v>135619982</v>
       </c>
       <c r="B28" t="n">
-        <v>79396</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3670,37 +3653,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679862</v>
+        <v>679625</v>
       </c>
       <c r="R28" t="n">
-        <v>7321960</v>
+        <v>7322249</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3729,7 +3720,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3739,14 +3730,19 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3765,49 +3761,54 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619961</t>
+          <t>https://artportalen.se/Sighting/135619982</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135619954</v>
+        <v>135637884</v>
       </c>
       <c r="B29" t="n">
-        <v>80267</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>266179</v>
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679703</v>
+        <v>679841</v>
       </c>
       <c r="R29" t="n">
-        <v>7321883</v>
+        <v>7322162</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3836,7 +3837,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3846,7 +3847,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3861,60 +3867,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619954</t>
+          <t>https://artportalen.se/Sighting/135637884</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135619980</v>
+        <v>135637885</v>
       </c>
       <c r="B30" t="n">
-        <v>80267</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>266179</v>
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679628</v>
+        <v>679690</v>
       </c>
       <c r="R30" t="n">
-        <v>7322239</v>
+        <v>7322205</v>
       </c>
       <c r="S30" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3943,7 +3954,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3953,7 +3964,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3968,16 +3984,1761 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637885</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135637886</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>679785</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7322109</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637886</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135637888</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>679854</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7322119</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>äldre bohål i en björk direkt under en (eld)ticka. På grund av den mycket runda formen och den lilla diametern (cirka 4 cm) skulle det mycket väl kunna vara gjort av en tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637888</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135637890</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>679438</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7322215</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack på gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637890</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135637892</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>679377</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7321710</v>
+      </c>
+      <c r="S34" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637892</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135649674</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>679561</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7322053</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>En ljudbox lämnades kvar på platsen, och det finns flera ljudinspelningar med både läten och trumningar som kan användas för att bekräfta fyndet.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649674</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135649680</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>679602</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7322064</v>
+      </c>
+      <c r="S36" t="n">
+        <v>12</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649680</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135619973</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>679752</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7322097</v>
+      </c>
+      <c r="S37" t="n">
+        <v>48</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619973</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135650299</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>679561</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7322053</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>enligt chirpity  57 upptäckter</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650299</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135619960</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>679846</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7321962</v>
+      </c>
+      <c r="S39" t="n">
+        <v>21</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619960</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135637879</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>679797</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7321975</v>
+      </c>
+      <c r="S40" t="n">
+        <v>8</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637879</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135619970</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80001</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>679752</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7322054</v>
+      </c>
+      <c r="S41" t="n">
+        <v>14</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619970</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135619974</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80001</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>679682</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7322160</v>
+      </c>
+      <c r="S42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619974</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135619961</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79434</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>679862</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7321960</v>
+      </c>
+      <c r="S43" t="n">
+        <v>11</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619961</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135619954</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80305</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>679703</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7321883</v>
+      </c>
+      <c r="S44" t="n">
+        <v>8</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619954</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135619980</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80305</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>679628</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7322239</v>
+      </c>
+      <c r="S45" t="n">
+        <v>33</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135619980</t>
         </is>
@@ -4014,6 +5775,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ45"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,7 +785,7 @@
         <v>135619959</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135619965</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135619977</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,48 +1118,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135619979</v>
+        <v>135637876</v>
       </c>
       <c r="B6" t="n">
-        <v>92195</v>
+        <v>91066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679635</v>
+        <v>679750</v>
       </c>
       <c r="R6" t="n">
-        <v>7322208</v>
+        <v>7321882</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,27 +1213,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619979</t>
+          <t>https://artportalen.se/Sighting/135637876</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135637876</v>
+        <v>135637880</v>
       </c>
       <c r="B7" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679750</v>
+        <v>679870</v>
       </c>
       <c r="R7" t="n">
-        <v>7321882</v>
+        <v>7322041</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,16 +1336,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637876</t>
+          <t>https://artportalen.se/Sighting/135637880</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135637880</v>
+        <v>135619967</v>
       </c>
       <c r="B8" t="n">
-        <v>91039</v>
+        <v>92096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,37 +1353,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679870</v>
+        <v>679755</v>
       </c>
       <c r="R8" t="n">
-        <v>7322041</v>
+        <v>7322069</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,27 +1437,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637880</t>
+          <t>https://artportalen.se/Sighting/135619967</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135619967</v>
+        <v>135619978</v>
       </c>
       <c r="B9" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679755</v>
+        <v>679637</v>
       </c>
       <c r="R9" t="n">
-        <v>7322069</v>
+        <v>7322205</v>
       </c>
       <c r="S9" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,16 +1560,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619967</t>
+          <t>https://artportalen.se/Sighting/135619978</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135619978</v>
+        <v>135637882</v>
       </c>
       <c r="B10" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,17 +1597,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>679637</v>
+        <v>679833</v>
       </c>
       <c r="R10" t="n">
-        <v>7322205</v>
+        <v>7322085</v>
       </c>
       <c r="S10" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,71 +1655,72 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619978</t>
+          <t>https://artportalen.se/Sighting/135637882</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135637882</v>
+        <v>135619962</v>
       </c>
       <c r="B11" t="n">
-        <v>92069</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679833</v>
+        <v>679861</v>
       </c>
       <c r="R11" t="n">
-        <v>7322085</v>
+        <v>7321962</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,56 +1768,55 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637882</t>
+          <t>https://artportalen.se/Sighting/135619962</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135619962</v>
+        <v>135619971</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>78841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679861</v>
+        <v>679746</v>
       </c>
       <c r="R12" t="n">
-        <v>7321962</v>
+        <v>7322048</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,16 +1897,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619962</t>
+          <t>https://artportalen.se/Sighting/135619971</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135619971</v>
+        <v>135619976</v>
       </c>
       <c r="B13" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679746</v>
+        <v>679673</v>
       </c>
       <c r="R13" t="n">
-        <v>7322048</v>
+        <v>7322179</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,16 +2009,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619971</t>
+          <t>https://artportalen.se/Sighting/135619976</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135619976</v>
+        <v>135637877</v>
       </c>
       <c r="B14" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,17 +2046,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679673</v>
+        <v>679736</v>
       </c>
       <c r="R14" t="n">
-        <v>7322179</v>
+        <v>7321943</v>
       </c>
       <c r="S14" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,27 +2110,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619976</t>
+          <t>https://artportalen.se/Sighting/135637877</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135637877</v>
+        <v>135619952</v>
       </c>
       <c r="B15" t="n">
-        <v>78814</v>
+        <v>80057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,37 +2138,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679736</v>
+        <v>679574</v>
       </c>
       <c r="R15" t="n">
-        <v>7321943</v>
+        <v>7321815</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,27 +2222,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637877</t>
+          <t>https://artportalen.se/Sighting/135619952</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135619952</v>
+        <v>135619958</v>
       </c>
       <c r="B16" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,13 +2274,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679574</v>
+        <v>679814</v>
       </c>
       <c r="R16" t="n">
-        <v>7321815</v>
+        <v>7321960</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,16 +2345,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619952</t>
+          <t>https://artportalen.se/Sighting/135619958</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135619958</v>
+        <v>135619969</v>
       </c>
       <c r="B17" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,13 +2386,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>679814</v>
+        <v>679744</v>
       </c>
       <c r="R17" t="n">
-        <v>7321960</v>
+        <v>7322052</v>
       </c>
       <c r="S17" t="n">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2457,16 +2457,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619958</t>
+          <t>https://artportalen.se/Sighting/135619969</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135619969</v>
+        <v>135619981</v>
       </c>
       <c r="B18" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679744</v>
+        <v>679630</v>
       </c>
       <c r="R18" t="n">
-        <v>7322052</v>
+        <v>7322240</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,16 +2569,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619969</t>
+          <t>https://artportalen.se/Sighting/135619981</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135619981</v>
+        <v>135637870</v>
       </c>
       <c r="B19" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,17 +2606,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679630</v>
+        <v>679550</v>
       </c>
       <c r="R19" t="n">
-        <v>7322240</v>
+        <v>7321796</v>
       </c>
       <c r="S19" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2670,27 +2670,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619981</t>
+          <t>https://artportalen.se/Sighting/135637870</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135637870</v>
+        <v>135619972</v>
       </c>
       <c r="B20" t="n">
-        <v>80030</v>
+        <v>78442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,37 +2698,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679550</v>
+        <v>679746</v>
       </c>
       <c r="R20" t="n">
-        <v>7321796</v>
+        <v>7322048</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2782,27 +2782,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637870</t>
+          <t>https://artportalen.se/Sighting/135619972</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135619972</v>
+        <v>135619975</v>
       </c>
       <c r="B21" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,13 +2834,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679746</v>
+        <v>679673</v>
       </c>
       <c r="R21" t="n">
-        <v>7322048</v>
+        <v>7322179</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2905,16 +2905,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619972</t>
+          <t>https://artportalen.se/Sighting/135619975</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135619975</v>
+        <v>135619953</v>
       </c>
       <c r="B22" t="n">
-        <v>78415</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,37 +2922,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>679673</v>
+        <v>679642</v>
       </c>
       <c r="R22" t="n">
-        <v>7322179</v>
+        <v>7321835</v>
       </c>
       <c r="S22" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2981,7 +2986,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2991,7 +2996,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,13 +3027,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619975</t>
+          <t>https://artportalen.se/Sighting/135619953</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135619953</v>
+        <v>135619957</v>
       </c>
       <c r="B23" t="n">
         <v>57980</v>
@@ -3052,24 +3062,27 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679642</v>
+        <v>679790</v>
       </c>
       <c r="R23" t="n">
-        <v>7321835</v>
+        <v>7321957</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3098,7 +3111,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3108,19 +3121,19 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3139,13 +3152,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619953</t>
+          <t>https://artportalen.se/Sighting/135619957</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135619957</v>
+        <v>135619963</v>
       </c>
       <c r="B24" t="n">
         <v>57980</v>
@@ -3188,13 +3201,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679790</v>
+        <v>679845</v>
       </c>
       <c r="R24" t="n">
-        <v>7321957</v>
+        <v>7322112</v>
       </c>
       <c r="S24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3223,7 +3236,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3246,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3264,13 +3277,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619957</t>
+          <t>https://artportalen.se/Sighting/135619963</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135619963</v>
+        <v>135619964</v>
       </c>
       <c r="B25" t="n">
         <v>57980</v>
@@ -3299,27 +3312,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679845</v>
+        <v>679863</v>
       </c>
       <c r="R25" t="n">
-        <v>7322112</v>
+        <v>7322052</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3348,7 +3358,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3358,19 +3368,19 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hackmärken från födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3389,13 +3399,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619963</t>
+          <t>https://artportalen.se/Sighting/135619964</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135619964</v>
+        <v>135619966</v>
       </c>
       <c r="B26" t="n">
         <v>57980</v>
@@ -3424,24 +3434,27 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679863</v>
+        <v>679785</v>
       </c>
       <c r="R26" t="n">
-        <v>7322052</v>
+        <v>7322100</v>
       </c>
       <c r="S26" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3470,7 +3483,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,19 +3493,19 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3511,13 +3524,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619964</t>
+          <t>https://artportalen.se/Sighting/135619966</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135619966</v>
+        <v>135619982</v>
       </c>
       <c r="B27" t="n">
         <v>57980</v>
@@ -3560,13 +3573,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679785</v>
+        <v>679625</v>
       </c>
       <c r="R27" t="n">
-        <v>7322100</v>
+        <v>7322249</v>
       </c>
       <c r="S27" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3595,7 +3608,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3605,7 +3618,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3636,13 +3649,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619966</t>
+          <t>https://artportalen.se/Sighting/135619982</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135619982</v>
+        <v>135637884</v>
       </c>
       <c r="B28" t="n">
         <v>57980</v>
@@ -3671,27 +3684,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679625</v>
+        <v>679841</v>
       </c>
       <c r="R28" t="n">
-        <v>7322249</v>
+        <v>7322162</v>
       </c>
       <c r="S28" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3720,7 +3725,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3730,19 +3735,19 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Hackmärken från födosök</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3750,24 +3755,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619982</t>
+          <t>https://artportalen.se/Sighting/135637884</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135637884</v>
+        <v>135637885</v>
       </c>
       <c r="B29" t="n">
         <v>57980</v>
@@ -3802,13 +3807,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679841</v>
+        <v>679690</v>
       </c>
       <c r="R29" t="n">
-        <v>7322162</v>
+        <v>7322205</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3837,7 +3842,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3847,7 +3852,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3878,13 +3883,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637884</t>
+          <t>https://artportalen.se/Sighting/135637885</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135637885</v>
+        <v>135637886</v>
       </c>
       <c r="B30" t="n">
         <v>57980</v>
@@ -3919,13 +3924,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679690</v>
+        <v>679785</v>
       </c>
       <c r="R30" t="n">
-        <v>7322205</v>
+        <v>7322109</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3954,7 +3959,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3964,19 +3969,19 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -3995,13 +4000,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637885</t>
+          <t>https://artportalen.se/Sighting/135637886</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135637886</v>
+        <v>135637888</v>
       </c>
       <c r="B31" t="n">
         <v>57980</v>
@@ -4036,10 +4041,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679785</v>
+        <v>679854</v>
       </c>
       <c r="R31" t="n">
-        <v>7322109</v>
+        <v>7322119</v>
       </c>
       <c r="S31" t="n">
         <v>6</v>
@@ -4071,7 +4076,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4081,12 +4086,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Hackspår på gran</t>
+          <t>äldre bohål i en björk direkt under en (eld)ticka. På grund av den mycket runda formen och den lilla diametern (cirka 4 cm) skulle det mycket väl kunna vara gjort av en tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4112,13 +4117,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637886</t>
+          <t>https://artportalen.se/Sighting/135637888</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135637888</v>
+        <v>135637890</v>
       </c>
       <c r="B32" t="n">
         <v>57980</v>
@@ -4153,13 +4158,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679854</v>
+        <v>679438</v>
       </c>
       <c r="R32" t="n">
-        <v>7322119</v>
+        <v>7322215</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4188,7 +4193,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4198,12 +4203,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>äldre bohål i en björk direkt under en (eld)ticka. På grund av den mycket runda formen och den lilla diametern (cirka 4 cm) skulle det mycket väl kunna vara gjort av en tretåig hackspett.</t>
+          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4229,13 +4234,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637888</t>
+          <t>https://artportalen.se/Sighting/135637890</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135637890</v>
+        <v>135637892</v>
       </c>
       <c r="B33" t="n">
         <v>57980</v>
@@ -4270,13 +4275,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679438</v>
+        <v>679377</v>
       </c>
       <c r="R33" t="n">
-        <v>7322215</v>
+        <v>7321710</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4305,7 +4310,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4315,19 +4320,19 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4346,13 +4351,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637890</t>
+          <t>https://artportalen.se/Sighting/135637892</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135637892</v>
+        <v>135649674</v>
       </c>
       <c r="B34" t="n">
         <v>57980</v>
@@ -4380,20 +4385,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679377</v>
+        <v>679561</v>
       </c>
       <c r="R34" t="n">
-        <v>7321710</v>
+        <v>7322053</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4417,27 +4426,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>En ljudbox lämnades kvar på platsen, och det finns flera ljudinspelningar med både läten och trumningar som kan användas för att bekräfta fyndet.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4463,13 +4472,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637892</t>
+          <t>https://artportalen.se/Sighting/135649674</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135649674</v>
+        <v>135649680</v>
       </c>
       <c r="B35" t="n">
         <v>57980</v>
@@ -4502,19 +4511,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679561</v>
+        <v>679602</v>
       </c>
       <c r="R35" t="n">
-        <v>7322053</v>
+        <v>7322064</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4538,27 +4559,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>En ljudbox lämnades kvar på platsen, och det finns flera ljudinspelningar med både läten och trumningar som kan användas för att bekräfta fyndet.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4584,16 +4600,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135649674</t>
+          <t>https://artportalen.se/Sighting/135649680</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135649680</v>
+        <v>135619973</v>
       </c>
       <c r="B36" t="n">
-        <v>57980</v>
+        <v>58141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,53 +4617,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679602</v>
+        <v>679752</v>
       </c>
       <c r="R36" t="n">
-        <v>7322064</v>
+        <v>7322097</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4701,24 +4701,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135649680</t>
+          <t>https://artportalen.se/Sighting/135619973</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135619973</v>
+        <v>135650299</v>
       </c>
       <c r="B37" t="n">
         <v>58141</v>
@@ -4747,19 +4747,31 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679752</v>
+        <v>679561</v>
       </c>
       <c r="R37" t="n">
-        <v>7322097</v>
+        <v>7322053</v>
       </c>
       <c r="S37" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4788,17 +4800,22 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>enligt chirpity  57 upptäckter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4813,27 +4830,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619973</t>
+          <t>https://artportalen.se/Sighting/135650299</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135650299</v>
+        <v>135619960</v>
       </c>
       <c r="B38" t="n">
-        <v>58141</v>
+        <v>58084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4841,49 +4858,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679561</v>
+        <v>679846</v>
       </c>
       <c r="R38" t="n">
-        <v>7322053</v>
+        <v>7321962</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4912,22 +4922,17 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>enligt chirpity  57 upptäckter</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4942,24 +4947,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135650299</t>
+          <t>https://artportalen.se/Sighting/135619960</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135619960</v>
+        <v>135637879</v>
       </c>
       <c r="B39" t="n">
         <v>58084</v>
@@ -4987,25 +4992,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679846</v>
+        <v>679797</v>
       </c>
       <c r="R39" t="n">
-        <v>7321962</v>
+        <v>7321975</v>
       </c>
       <c r="S39" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5034,7 +5042,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5044,7 +5052,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5059,27 +5067,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619960</t>
+          <t>https://artportalen.se/Sighting/135637879</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135637879</v>
+        <v>135619970</v>
       </c>
       <c r="B40" t="n">
-        <v>58084</v>
+        <v>80028</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5087,45 +5095,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679797</v>
+        <v>679752</v>
       </c>
       <c r="R40" t="n">
-        <v>7321975</v>
+        <v>7322054</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5179,27 +5179,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637879</t>
+          <t>https://artportalen.se/Sighting/135619970</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135619970</v>
+        <v>135619974</v>
       </c>
       <c r="B41" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5231,13 +5231,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679752</v>
+        <v>679682</v>
       </c>
       <c r="R41" t="n">
-        <v>7322054</v>
+        <v>7322160</v>
       </c>
       <c r="S41" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5302,16 +5302,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619970</t>
+          <t>https://artportalen.se/Sighting/135619974</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135619974</v>
+        <v>135619961</v>
       </c>
       <c r="B42" t="n">
-        <v>80001</v>
+        <v>79461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5319,21 +5319,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5343,13 +5343,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679682</v>
+        <v>679862</v>
       </c>
       <c r="R42" t="n">
-        <v>7322160</v>
+        <v>7321960</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5414,38 +5414,33 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619974</t>
+          <t>https://artportalen.se/Sighting/135619961</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135619961</v>
+        <v>135619954</v>
       </c>
       <c r="B43" t="n">
-        <v>79434</v>
+        <v>80332</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
+        <v>266179</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lecidea subhumida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Vain.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5455,13 +5450,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679862</v>
+        <v>679703</v>
       </c>
       <c r="R43" t="n">
-        <v>7321960</v>
+        <v>7321883</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5490,7 +5485,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5500,7 +5495,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5526,16 +5521,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619961</t>
+          <t>https://artportalen.se/Sighting/135619954</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135619954</v>
+        <v>135619980</v>
       </c>
       <c r="B44" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5562,13 +5557,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679703</v>
+        <v>679628</v>
       </c>
       <c r="R44" t="n">
-        <v>7321883</v>
+        <v>7322239</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5597,7 +5592,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5607,7 +5602,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5632,113 +5627,6 @@
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135619954</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>135619980</v>
-      </c>
-      <c r="B45" t="n">
-        <v>80305</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>266179</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Lecidea subhumida</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Vain.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Norrstrand, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>679628</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7322239</v>
-      </c>
-      <c r="S45" t="n">
-        <v>33</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135619980</t>
         </is>
@@ -5789,7 +5677,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,9 +780,4911 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135619959</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>353</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>679812</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7321979</v>
+      </c>
+      <c r="S3" t="n">
+        <v>27</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619959</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135619965</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>679806</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7322095</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619965</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135619977</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>679670</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7322193</v>
+      </c>
+      <c r="S5" t="n">
+        <v>69</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619977</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135637876</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91069</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>679750</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7321882</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637876</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135637880</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91069</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>679870</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7322041</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637880</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135619967</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>679755</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7322069</v>
+      </c>
+      <c r="S8" t="n">
+        <v>17</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619967</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135619978</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>679637</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7322205</v>
+      </c>
+      <c r="S9" t="n">
+        <v>43</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619978</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135637882</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>679833</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7322085</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637882</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135619962</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>679861</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7321962</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619962</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135619971</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>679746</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7322048</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619971</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135619976</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>679673</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7322179</v>
+      </c>
+      <c r="S13" t="n">
+        <v>68</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619976</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135637877</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>679736</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7321943</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637877</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135619952</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>679574</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7321815</v>
+      </c>
+      <c r="S15" t="n">
+        <v>14</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619952</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135619958</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>679814</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7321960</v>
+      </c>
+      <c r="S16" t="n">
+        <v>96</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619958</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135619969</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>679744</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7322052</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619969</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135619981</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>679630</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7322240</v>
+      </c>
+      <c r="S18" t="n">
+        <v>22</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619981</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135637870</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>679550</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7321796</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637870</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135619972</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>679746</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7322048</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619972</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135619975</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>679673</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7322179</v>
+      </c>
+      <c r="S21" t="n">
+        <v>64</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619975</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135619953</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>679642</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7321835</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619953</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135619957</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>679790</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7321957</v>
+      </c>
+      <c r="S23" t="n">
+        <v>16</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619957</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135619963</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>679845</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7322112</v>
+      </c>
+      <c r="S24" t="n">
+        <v>12</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619963</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135619964</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>679863</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7322052</v>
+      </c>
+      <c r="S25" t="n">
+        <v>22</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619964</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135619966</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>679785</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7322100</v>
+      </c>
+      <c r="S26" t="n">
+        <v>44</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619966</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135619982</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>679625</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7322249</v>
+      </c>
+      <c r="S27" t="n">
+        <v>41</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619982</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135637884</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>679841</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7322162</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637884</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135637885</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>679690</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7322205</v>
+      </c>
+      <c r="S29" t="n">
+        <v>7</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637885</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135637886</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>679785</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7322109</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637886</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135637888</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>679854</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7322119</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>äldre bohål i en björk direkt under en (eld)ticka. På grund av den mycket runda formen och den lilla diametern (cirka 4 cm) skulle det mycket väl kunna vara gjort av en tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637888</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135637890</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>679438</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7322215</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>fodersök på gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637890</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135637892</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>679377</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7321710</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637892</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135649674</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>679561</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7322053</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ljudinspelningar med både läten och trumningar finns</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649674</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135649680</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>679602</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7322064</v>
+      </c>
+      <c r="S35" t="n">
+        <v>12</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649680</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135619973</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>679752</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7322097</v>
+      </c>
+      <c r="S36" t="n">
+        <v>48</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619973</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135650299</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>679561</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7322053</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>ljudinspelning finns</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650299</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135619960</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>679846</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7321962</v>
+      </c>
+      <c r="S38" t="n">
+        <v>21</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619960</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135637879</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>679797</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7321975</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637879</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135619970</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>679752</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7322054</v>
+      </c>
+      <c r="S40" t="n">
+        <v>14</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619970</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135619974</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>679682</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7322160</v>
+      </c>
+      <c r="S41" t="n">
+        <v>7</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619974</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135619961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>679862</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7321960</v>
+      </c>
+      <c r="S42" t="n">
+        <v>11</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619961</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135619954</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>679703</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7321883</v>
+      </c>
+      <c r="S43" t="n">
+        <v>8</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619954</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135619980</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>679628</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7322239</v>
+      </c>
+      <c r="S44" t="n">
+        <v>33</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619980</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -1009,7 +1009,7 @@
         <v>135619977</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135637876</v>
       </c>
       <c r="B6" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135637880</v>
       </c>
       <c r="B7" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135619967</v>
       </c>
       <c r="B8" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135619978</v>
       </c>
       <c r="B9" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135637882</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ44"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135619977</v>
+        <v>135952415</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>79520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,37 +1017,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679670</v>
+        <v>679841</v>
       </c>
       <c r="R5" t="n">
-        <v>7322193</v>
+        <v>7322053</v>
       </c>
       <c r="S5" t="n">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,33 +1095,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619977</t>
+          <t>https://artportalen.se/Sighting/135952415</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135637876</v>
+        <v>135619977</v>
       </c>
       <c r="B6" t="n">
-        <v>91071</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,37 +1130,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679750</v>
+        <v>679670</v>
       </c>
       <c r="R6" t="n">
-        <v>7321882</v>
+        <v>7322193</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,27 +1214,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637876</t>
+          <t>https://artportalen.se/Sighting/135619977</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135637880</v>
+        <v>135952413</v>
       </c>
       <c r="B7" t="n">
-        <v>91071</v>
+        <v>92243</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1242,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>1588</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,13 +1266,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679870</v>
+        <v>679476</v>
       </c>
       <c r="R7" t="n">
-        <v>7322041</v>
+        <v>7322162</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,22 +1296,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,16 +1337,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637880</t>
+          <t>https://artportalen.se/Sighting/135952413</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135619967</v>
+        <v>135637876</v>
       </c>
       <c r="B8" t="n">
-        <v>92103</v>
+        <v>91071</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,37 +1354,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679755</v>
+        <v>679750</v>
       </c>
       <c r="R8" t="n">
-        <v>7322069</v>
+        <v>7321882</v>
       </c>
       <c r="S8" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,27 +1438,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619967</t>
+          <t>https://artportalen.se/Sighting/135637876</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135619978</v>
+        <v>135637880</v>
       </c>
       <c r="B9" t="n">
-        <v>92103</v>
+        <v>91071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,37 +1466,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679637</v>
+        <v>679870</v>
       </c>
       <c r="R9" t="n">
-        <v>7322205</v>
+        <v>7322041</v>
       </c>
       <c r="S9" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,24 +1550,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619978</t>
+          <t>https://artportalen.se/Sighting/135637880</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135637882</v>
+        <v>135619967</v>
       </c>
       <c r="B10" t="n">
         <v>92103</v>
@@ -1597,17 +1598,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>679833</v>
+        <v>679755</v>
       </c>
       <c r="R10" t="n">
-        <v>7322085</v>
+        <v>7322069</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1647,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,56 +1656,55 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637882</t>
+          <t>https://artportalen.se/Sighting/135619967</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135619962</v>
+        <v>135619978</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>92103</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679861</v>
+        <v>679637</v>
       </c>
       <c r="R11" t="n">
-        <v>7321962</v>
+        <v>7322205</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,16 +1785,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619962</t>
+          <t>https://artportalen.se/Sighting/135619978</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135619971</v>
+        <v>135637882</v>
       </c>
       <c r="B12" t="n">
-        <v>78844</v>
+        <v>92103</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,37 +1802,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679746</v>
+        <v>679833</v>
       </c>
       <c r="R12" t="n">
-        <v>7322048</v>
+        <v>7322085</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,55 +1880,56 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619971</t>
+          <t>https://artportalen.se/Sighting/135637882</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135619976</v>
+        <v>135619962</v>
       </c>
       <c r="B13" t="n">
-        <v>78844</v>
+        <v>79441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1938,13 +1939,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679673</v>
+        <v>679861</v>
       </c>
       <c r="R13" t="n">
-        <v>7322179</v>
+        <v>7321962</v>
       </c>
       <c r="S13" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1983,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,13 +2010,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619976</t>
+          <t>https://artportalen.se/Sighting/135619962</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135637877</v>
+        <v>135619971</v>
       </c>
       <c r="B14" t="n">
         <v>78844</v>
@@ -2046,17 +2047,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679736</v>
+        <v>679746</v>
       </c>
       <c r="R14" t="n">
-        <v>7321943</v>
+        <v>7322048</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2085,7 +2086,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2095,7 +2096,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,27 +2111,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637877</t>
+          <t>https://artportalen.se/Sighting/135619971</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135619952</v>
+        <v>135619976</v>
       </c>
       <c r="B15" t="n">
-        <v>80060</v>
+        <v>78844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,21 +2139,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,13 +2163,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679574</v>
+        <v>679673</v>
       </c>
       <c r="R15" t="n">
-        <v>7321815</v>
+        <v>7322179</v>
       </c>
       <c r="S15" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2197,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2207,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,16 +2234,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619952</t>
+          <t>https://artportalen.se/Sighting/135619976</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135619958</v>
+        <v>135637877</v>
       </c>
       <c r="B16" t="n">
-        <v>80060</v>
+        <v>78844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,37 +2251,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679814</v>
+        <v>679736</v>
       </c>
       <c r="R16" t="n">
-        <v>7321960</v>
+        <v>7321943</v>
       </c>
       <c r="S16" t="n">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2309,7 +2310,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2319,7 +2320,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2334,24 +2335,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619958</t>
+          <t>https://artportalen.se/Sighting/135637877</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135619969</v>
+        <v>135619952</v>
       </c>
       <c r="B17" t="n">
         <v>80060</v>
@@ -2386,13 +2387,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>679744</v>
+        <v>679574</v>
       </c>
       <c r="R17" t="n">
-        <v>7322052</v>
+        <v>7321815</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2421,7 +2422,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2431,7 +2432,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2457,13 +2458,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619969</t>
+          <t>https://artportalen.se/Sighting/135619952</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135619981</v>
+        <v>135619958</v>
       </c>
       <c r="B18" t="n">
         <v>80060</v>
@@ -2498,13 +2499,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679630</v>
+        <v>679814</v>
       </c>
       <c r="R18" t="n">
-        <v>7322240</v>
+        <v>7321960</v>
       </c>
       <c r="S18" t="n">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2543,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,13 +2570,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619981</t>
+          <t>https://artportalen.se/Sighting/135619958</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135637870</v>
+        <v>135619969</v>
       </c>
       <c r="B19" t="n">
         <v>80060</v>
@@ -2606,17 +2607,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679550</v>
+        <v>679744</v>
       </c>
       <c r="R19" t="n">
-        <v>7321796</v>
+        <v>7322052</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2645,7 +2646,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2655,7 +2656,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2670,27 +2671,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637870</t>
+          <t>https://artportalen.se/Sighting/135619969</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135619972</v>
+        <v>135619981</v>
       </c>
       <c r="B20" t="n">
-        <v>78445</v>
+        <v>80060</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,21 +2699,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,13 +2723,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679746</v>
+        <v>679630</v>
       </c>
       <c r="R20" t="n">
-        <v>7322048</v>
+        <v>7322240</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2757,7 +2758,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2767,7 +2768,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2793,16 +2794,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619972</t>
+          <t>https://artportalen.se/Sighting/135619981</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135619975</v>
+        <v>135637870</v>
       </c>
       <c r="B21" t="n">
-        <v>78445</v>
+        <v>80060</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,37 +2811,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679673</v>
+        <v>679550</v>
       </c>
       <c r="R21" t="n">
-        <v>7322179</v>
+        <v>7321796</v>
       </c>
       <c r="S21" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2869,7 +2870,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2879,7 +2880,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2894,27 +2895,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619975</t>
+          <t>https://artportalen.se/Sighting/135637870</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135619953</v>
+        <v>135619972</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>78445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,42 +2923,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>679642</v>
+        <v>679746</v>
       </c>
       <c r="R22" t="n">
-        <v>7321835</v>
+        <v>7322048</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2986,7 +2982,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2996,12 +2992,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,16 +3018,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619953</t>
+          <t>https://artportalen.se/Sighting/135619972</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135619957</v>
+        <v>135619975</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>78445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,45 +3035,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679790</v>
+        <v>679673</v>
       </c>
       <c r="R23" t="n">
-        <v>7321957</v>
+        <v>7322179</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3111,7 +3094,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,19 +3104,14 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3152,13 +3130,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619957</t>
+          <t>https://artportalen.se/Sighting/135619975</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135619963</v>
+        <v>135619953</v>
       </c>
       <c r="B24" t="n">
         <v>57980</v>
@@ -3187,27 +3165,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679845</v>
+        <v>679642</v>
       </c>
       <c r="R24" t="n">
-        <v>7322112</v>
+        <v>7321835</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3236,7 +3211,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3246,19 +3221,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Hackmärken från födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3277,13 +3252,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619963</t>
+          <t>https://artportalen.se/Sighting/135619953</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135619964</v>
+        <v>135619957</v>
       </c>
       <c r="B25" t="n">
         <v>57980</v>
@@ -3312,24 +3287,27 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679863</v>
+        <v>679790</v>
       </c>
       <c r="R25" t="n">
-        <v>7322052</v>
+        <v>7321957</v>
       </c>
       <c r="S25" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3358,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3368,19 +3346,19 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3399,13 +3377,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619964</t>
+          <t>https://artportalen.se/Sighting/135619957</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135619966</v>
+        <v>135619963</v>
       </c>
       <c r="B26" t="n">
         <v>57980</v>
@@ -3448,13 +3426,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679785</v>
+        <v>679845</v>
       </c>
       <c r="R26" t="n">
-        <v>7322100</v>
+        <v>7322112</v>
       </c>
       <c r="S26" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3483,7 +3461,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3493,7 +3471,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3524,13 +3502,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619966</t>
+          <t>https://artportalen.se/Sighting/135619963</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135619982</v>
+        <v>135619964</v>
       </c>
       <c r="B27" t="n">
         <v>57980</v>
@@ -3559,27 +3537,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679625</v>
+        <v>679863</v>
       </c>
       <c r="R27" t="n">
-        <v>7322249</v>
+        <v>7322052</v>
       </c>
       <c r="S27" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3608,7 +3583,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3618,19 +3593,19 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hackmärken från födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3649,13 +3624,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619982</t>
+          <t>https://artportalen.se/Sighting/135619964</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135637884</v>
+        <v>135619966</v>
       </c>
       <c r="B28" t="n">
         <v>57980</v>
@@ -3684,19 +3659,27 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679841</v>
+        <v>679785</v>
       </c>
       <c r="R28" t="n">
-        <v>7322162</v>
+        <v>7322100</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3725,7 +3708,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3735,19 +3718,19 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3755,24 +3738,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637884</t>
+          <t>https://artportalen.se/Sighting/135619966</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135637885</v>
+        <v>135619982</v>
       </c>
       <c r="B29" t="n">
         <v>57980</v>
@@ -3801,19 +3784,27 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679690</v>
+        <v>679625</v>
       </c>
       <c r="R29" t="n">
-        <v>7322205</v>
+        <v>7322249</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3842,7 +3833,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3852,19 +3843,19 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -3872,24 +3863,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637885</t>
+          <t>https://artportalen.se/Sighting/135619982</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135637886</v>
+        <v>135637884</v>
       </c>
       <c r="B30" t="n">
         <v>57980</v>
@@ -3924,13 +3915,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679785</v>
+        <v>679841</v>
       </c>
       <c r="R30" t="n">
-        <v>7322109</v>
+        <v>7322162</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3959,7 +3950,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3969,19 +3960,19 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Hackspår på gran</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -4000,13 +3991,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637886</t>
+          <t>https://artportalen.se/Sighting/135637884</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135637888</v>
+        <v>135637885</v>
       </c>
       <c r="B31" t="n">
         <v>57980</v>
@@ -4041,13 +4032,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679854</v>
+        <v>679690</v>
       </c>
       <c r="R31" t="n">
-        <v>7322119</v>
+        <v>7322205</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4076,7 +4067,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4086,19 +4077,19 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>äldre bohål i en björk direkt under en (eld)ticka. På grund av den mycket runda formen och den lilla diametern (cirka 4 cm) skulle det mycket väl kunna vara gjort av en tretåig hackspett.</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="b">
         <v>0</v>
@@ -4117,13 +4108,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637888</t>
+          <t>https://artportalen.se/Sighting/135637885</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135637890</v>
+        <v>135637886</v>
       </c>
       <c r="B32" t="n">
         <v>57980</v>
@@ -4152,27 +4143,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679438</v>
+        <v>679785</v>
       </c>
       <c r="R32" t="n">
-        <v>7322215</v>
+        <v>7322109</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4201,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4211,12 +4194,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>fodersök på gran</t>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4242,13 +4225,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637890</t>
+          <t>https://artportalen.se/Sighting/135637886</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135637892</v>
+        <v>135637888</v>
       </c>
       <c r="B33" t="n">
         <v>57980</v>
@@ -4283,13 +4266,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679377</v>
+        <v>679854</v>
       </c>
       <c r="R33" t="n">
-        <v>7321710</v>
+        <v>7322119</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4318,7 +4301,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4328,19 +4311,19 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>äldre bohål i en björk direkt under en (eld)ticka. På grund av den mycket runda formen och den lilla diametern (cirka 4 cm) skulle det mycket väl kunna vara gjort av en tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4359,13 +4342,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637892</t>
+          <t>https://artportalen.se/Sighting/135637888</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135649674</v>
+        <v>135637890</v>
       </c>
       <c r="B34" t="n">
         <v>57980</v>
@@ -4393,14 +4376,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4408,10 +4391,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679561</v>
+        <v>679438</v>
       </c>
       <c r="R34" t="n">
-        <v>7322053</v>
+        <v>7322215</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4438,34 +4421,34 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ljudinspelningar med både läten och trumningar finns</t>
+          <t>fodersök på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4484,13 +4467,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135649674</t>
+          <t>https://artportalen.se/Sighting/135637890</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135649680</v>
+        <v>135637892</v>
       </c>
       <c r="B35" t="n">
         <v>57980</v>
@@ -4518,36 +4501,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679602</v>
+        <v>679377</v>
       </c>
       <c r="R35" t="n">
-        <v>7322064</v>
+        <v>7321710</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4576,7 +4543,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4586,7 +4553,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4612,16 +4584,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135649680</t>
+          <t>https://artportalen.se/Sighting/135637892</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135619973</v>
+        <v>135649674</v>
       </c>
       <c r="B36" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4629,37 +4601,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679752</v>
+        <v>679561</v>
       </c>
       <c r="R36" t="n">
-        <v>7322097</v>
+        <v>7322053</v>
       </c>
       <c r="S36" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4683,22 +4663,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ljudinspelningar med både läten och trumningar finns</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4713,27 +4698,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619973</t>
+          <t>https://artportalen.se/Sighting/135649674</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135650299</v>
+        <v>135649680</v>
       </c>
       <c r="B37" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4741,45 +4726,53 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679561</v>
+        <v>679602</v>
       </c>
       <c r="R37" t="n">
-        <v>7322053</v>
+        <v>7322064</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4808,22 +4801,17 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>ljudinspelning finns</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4849,16 +4837,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135650299</t>
+          <t>https://artportalen.se/Sighting/135649680</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135619960</v>
+        <v>135952178</v>
       </c>
       <c r="B38" t="n">
-        <v>58084</v>
+        <v>57980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4866,16 +4854,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4884,24 +4872,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke3, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679846</v>
+        <v>679843</v>
       </c>
       <c r="R38" t="n">
-        <v>7321962</v>
+        <v>7322138</v>
       </c>
       <c r="S38" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4925,22 +4908,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4955,27 +4943,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619960</t>
+          <t>https://artportalen.se/Sighting/135952178</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135637879</v>
+        <v>135952414</v>
       </c>
       <c r="B39" t="n">
-        <v>58084</v>
+        <v>57980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4983,16 +4971,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5000,28 +4988,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679797</v>
+        <v>679677</v>
       </c>
       <c r="R39" t="n">
-        <v>7321975</v>
+        <v>7322293</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5045,29 +5025,34 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska spår fodersök</t>
         </is>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG39" t="b">
         <v>0</v>
@@ -5086,16 +5071,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637879</t>
+          <t>https://artportalen.se/Sighting/135952414</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135619970</v>
+        <v>135952417</v>
       </c>
       <c r="B40" t="n">
-        <v>80031</v>
+        <v>57980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5103,37 +5088,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679752</v>
+        <v>679684</v>
       </c>
       <c r="R40" t="n">
-        <v>7322054</v>
+        <v>7321810</v>
       </c>
       <c r="S40" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5157,22 +5150,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>ringhack tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5187,27 +5185,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619970</t>
+          <t>https://artportalen.se/Sighting/135952417</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135619974</v>
+        <v>135952418</v>
       </c>
       <c r="B41" t="n">
-        <v>80031</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5215,34 +5213,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679682</v>
+        <v>679649</v>
       </c>
       <c r="R41" t="n">
-        <v>7322160</v>
+        <v>7321825</v>
       </c>
       <c r="S41" t="n">
         <v>7</v>
@@ -5269,22 +5267,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5299,27 +5302,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619974</t>
+          <t>https://artportalen.se/Sighting/135952418</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135619961</v>
+        <v>135619973</v>
       </c>
       <c r="B42" t="n">
-        <v>79464</v>
+        <v>58141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,21 +5330,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5351,13 +5354,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679862</v>
+        <v>679752</v>
       </c>
       <c r="R42" t="n">
-        <v>7321960</v>
+        <v>7322097</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5386,7 +5389,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5399,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5422,49 +5425,62 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619961</t>
+          <t>https://artportalen.se/Sighting/135619973</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135619954</v>
+        <v>135650299</v>
       </c>
       <c r="B43" t="n">
-        <v>80335</v>
+        <v>58141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>266179</v>
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679703</v>
+        <v>679561</v>
       </c>
       <c r="R43" t="n">
-        <v>7321883</v>
+        <v>7322053</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5493,17 +5509,22 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ljudinspelning finns</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5518,60 +5539,70 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619954</t>
+          <t>https://artportalen.se/Sighting/135650299</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135619980</v>
+        <v>135619960</v>
       </c>
       <c r="B44" t="n">
-        <v>80335</v>
+        <v>58084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>266179</v>
+        <v>103031</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679628</v>
+        <v>679846</v>
       </c>
       <c r="R44" t="n">
-        <v>7322239</v>
+        <v>7321962</v>
       </c>
       <c r="S44" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5600,7 +5631,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5610,7 +5641,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5635,6 +5666,676 @@
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619960</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135637879</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>679797</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7321975</v>
+      </c>
+      <c r="S45" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637879</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135619970</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>679752</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7322054</v>
+      </c>
+      <c r="S46" t="n">
+        <v>14</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619970</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135619974</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>679682</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7322160</v>
+      </c>
+      <c r="S47" t="n">
+        <v>7</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619974</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135619961</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>679862</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7321960</v>
+      </c>
+      <c r="S48" t="n">
+        <v>11</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619961</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135619954</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>679703</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7321883</v>
+      </c>
+      <c r="S49" t="n">
+        <v>8</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619954</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135619980</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>679628</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7322239</v>
+      </c>
+      <c r="S50" t="n">
+        <v>33</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135619980</t>
         </is>
@@ -5685,6 +6386,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135619959</v>
       </c>
       <c r="B3" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135619965</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135952415</v>
       </c>
       <c r="B5" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>135619977</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>135952413</v>
       </c>
       <c r="B7" t="n">
-        <v>92243</v>
+        <v>92257</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>135637876</v>
       </c>
       <c r="B8" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135637880</v>
       </c>
       <c r="B9" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>135619967</v>
       </c>
       <c r="B10" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>135619978</v>
       </c>
       <c r="B11" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>135637882</v>
       </c>
       <c r="B12" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135619962</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>135619971</v>
       </c>
       <c r="B14" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>135619976</v>
       </c>
       <c r="B15" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>135637877</v>
       </c>
       <c r="B16" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>135619952</v>
       </c>
       <c r="B17" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>135619958</v>
       </c>
       <c r="B18" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>135619969</v>
       </c>
       <c r="B19" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>135619981</v>
       </c>
       <c r="B20" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>135637870</v>
       </c>
       <c r="B21" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>135619972</v>
       </c>
       <c r="B22" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>135619975</v>
       </c>
       <c r="B23" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135619953</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>135619957</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>135619963</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>135619964</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>135619966</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135619982</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>135637884</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>135637885</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>135637886</v>
       </c>
       <c r="B32" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>135637888</v>
       </c>
       <c r="B33" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>135637890</v>
       </c>
       <c r="B34" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>135637892</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135649674</v>
       </c>
       <c r="B36" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>135649680</v>
       </c>
       <c r="B37" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>135952178</v>
       </c>
       <c r="B38" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>135952414</v>
       </c>
       <c r="B39" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>135952417</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>135952418</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>135619973</v>
       </c>
       <c r="B42" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>135650299</v>
       </c>
       <c r="B43" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>135619960</v>
       </c>
       <c r="B44" t="n">
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>135637879</v>
       </c>
       <c r="B45" t="n">
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>135619970</v>
       </c>
       <c r="B46" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>135619974</v>
       </c>
       <c r="B47" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>135619961</v>
       </c>
       <c r="B48" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>135619954</v>
       </c>
       <c r="B49" t="n">
-        <v>80335</v>
+        <v>80337</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>135619980</v>
       </c>
       <c r="B50" t="n">
-        <v>80335</v>
+        <v>80337</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ50"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98308452</v>
+        <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Suöbdieke, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679637</v>
+        <v>679406</v>
       </c>
       <c r="R2" t="n">
-        <v>7322204</v>
+        <v>7321921</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,71 +772,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98308452</t>
+          <t>https://artportalen.se/Sighting/136146424</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135619959</v>
+        <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>79109</v>
+        <v>92311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679812</v>
+        <v>679446</v>
       </c>
       <c r="R3" t="n">
-        <v>7321979</v>
+        <v>7321904</v>
       </c>
       <c r="S3" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,27 +891,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619959</t>
+          <t>https://artportalen.se/Sighting/136146435</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135619965</v>
+        <v>98308452</v>
       </c>
       <c r="B4" t="n">
-        <v>79109</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,17 +939,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Suöbdieke, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679806</v>
+        <v>679637</v>
       </c>
       <c r="R4" t="n">
-        <v>7322095</v>
+        <v>7322204</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,22 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,27 +993,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619965</t>
+          <t>https://artportalen.se/Sighting/98308452</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135952415</v>
+        <v>135619959</v>
       </c>
       <c r="B5" t="n">
-        <v>79522</v>
+        <v>79109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,37 +1021,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679841</v>
+        <v>679812</v>
       </c>
       <c r="R5" t="n">
-        <v>7322053</v>
+        <v>7321979</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1075,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,34 +1099,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135952415</t>
+          <t>https://artportalen.se/Sighting/135619959</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135619977</v>
+        <v>135619965</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>79109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679670</v>
+        <v>679806</v>
       </c>
       <c r="R6" t="n">
-        <v>7322193</v>
+        <v>7322095</v>
       </c>
       <c r="S6" t="n">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,16 +1228,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619977</t>
+          <t>https://artportalen.se/Sighting/135619965</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135952413</v>
+        <v>136146432</v>
       </c>
       <c r="B7" t="n">
-        <v>92257</v>
+        <v>79110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1588</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,13 +1269,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679476</v>
+        <v>679429</v>
       </c>
       <c r="R7" t="n">
-        <v>7322162</v>
+        <v>7321823</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,22 +1299,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,6 +1323,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1337,16 +1341,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135952413</t>
+          <t>https://artportalen.se/Sighting/136146432</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135637876</v>
+        <v>136146442</v>
       </c>
       <c r="B8" t="n">
-        <v>91073</v>
+        <v>79110</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,13 +1382,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679750</v>
+        <v>679806</v>
       </c>
       <c r="R8" t="n">
-        <v>7321882</v>
+        <v>7321983</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1408,22 +1412,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,6 +1436,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1449,16 +1454,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637876</t>
+          <t>https://artportalen.se/Sighting/136146442</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135637880</v>
+        <v>135952415</v>
       </c>
       <c r="B9" t="n">
-        <v>91073</v>
+        <v>79522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,21 +1471,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,13 +1495,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679870</v>
+        <v>679841</v>
       </c>
       <c r="R9" t="n">
-        <v>7322041</v>
+        <v>7322053</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,22 +1525,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,6 +1549,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1561,16 +1567,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637880</t>
+          <t>https://artportalen.se/Sighting/135952415</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135619967</v>
+        <v>135619977</v>
       </c>
       <c r="B10" t="n">
-        <v>92117</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,21 +1584,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,13 +1608,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>679755</v>
+        <v>679670</v>
       </c>
       <c r="R10" t="n">
-        <v>7322069</v>
+        <v>7322193</v>
       </c>
       <c r="S10" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,7 +1643,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1653,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,16 +1679,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619967</t>
+          <t>https://artportalen.se/Sighting/135619977</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135619978</v>
+        <v>135952413</v>
       </c>
       <c r="B11" t="n">
-        <v>92117</v>
+        <v>92257</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,37 +1696,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>1588</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679637</v>
+        <v>679476</v>
       </c>
       <c r="R11" t="n">
-        <v>7322205</v>
+        <v>7322162</v>
       </c>
       <c r="S11" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,22 +1750,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,27 +1780,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619978</t>
+          <t>https://artportalen.se/Sighting/135952413</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135637882</v>
+        <v>135637876</v>
       </c>
       <c r="B12" t="n">
-        <v>92117</v>
+        <v>91073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1808,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,13 +1832,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679833</v>
+        <v>679750</v>
       </c>
       <c r="R12" t="n">
-        <v>7322085</v>
+        <v>7321882</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,7 +1886,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1898,54 +1903,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637882</t>
+          <t>https://artportalen.se/Sighting/135637876</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135619962</v>
+        <v>135637880</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>91073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679861</v>
+        <v>679870</v>
       </c>
       <c r="R13" t="n">
-        <v>7321962</v>
+        <v>7322041</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1989,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,27 +2004,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619962</t>
+          <t>https://artportalen.se/Sighting/135637880</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135619971</v>
+        <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>78846</v>
+        <v>91074</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,37 +2032,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679746</v>
+        <v>679397</v>
       </c>
       <c r="R14" t="n">
-        <v>7322048</v>
+        <v>7321944</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2081,22 +2086,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Und eier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,27 +2121,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619971</t>
+          <t>https://artportalen.se/Sighting/136146422</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135619976</v>
+        <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>78846</v>
+        <v>91074</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2139,37 +2149,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679673</v>
+        <v>679399</v>
       </c>
       <c r="R15" t="n">
-        <v>7322179</v>
+        <v>7321802</v>
       </c>
       <c r="S15" t="n">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,22 +2203,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,27 +2233,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619976</t>
+          <t>https://artportalen.se/Sighting/136146428</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135637877</v>
+        <v>135619967</v>
       </c>
       <c r="B16" t="n">
-        <v>78846</v>
+        <v>92117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,37 +2261,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679736</v>
+        <v>679755</v>
       </c>
       <c r="R16" t="n">
-        <v>7321943</v>
+        <v>7322069</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2310,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2320,7 +2330,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,27 +2345,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637877</t>
+          <t>https://artportalen.se/Sighting/135619967</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135619952</v>
+        <v>135619978</v>
       </c>
       <c r="B17" t="n">
-        <v>80062</v>
+        <v>92117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,21 +2373,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2387,13 +2397,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>679574</v>
+        <v>679637</v>
       </c>
       <c r="R17" t="n">
-        <v>7321815</v>
+        <v>7322205</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2422,7 +2432,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2432,7 +2442,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,16 +2468,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619952</t>
+          <t>https://artportalen.se/Sighting/135619978</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135619958</v>
+        <v>135637882</v>
       </c>
       <c r="B18" t="n">
-        <v>80062</v>
+        <v>92117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,37 +2485,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679814</v>
+        <v>679833</v>
       </c>
       <c r="R18" t="n">
-        <v>7321960</v>
+        <v>7322085</v>
       </c>
       <c r="S18" t="n">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2534,7 +2544,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2554,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,71 +2563,72 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619958</t>
+          <t>https://artportalen.se/Sighting/135637882</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135619969</v>
+        <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>80062</v>
+        <v>92028</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679744</v>
+        <v>679448</v>
       </c>
       <c r="R19" t="n">
-        <v>7322052</v>
+        <v>7321904</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,22 +2652,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,49 +2682,49 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619969</t>
+          <t>https://artportalen.se/Sighting/136146434</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135619981</v>
+        <v>135619962</v>
       </c>
       <c r="B20" t="n">
-        <v>80062</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2723,13 +2734,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679630</v>
+        <v>679861</v>
       </c>
       <c r="R20" t="n">
-        <v>7322240</v>
+        <v>7321962</v>
       </c>
       <c r="S20" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2758,7 +2769,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2768,7 +2779,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2794,16 +2805,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619981</t>
+          <t>https://artportalen.se/Sighting/135619962</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135637870</v>
+        <v>135619971</v>
       </c>
       <c r="B21" t="n">
-        <v>80062</v>
+        <v>78846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2811,37 +2822,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679550</v>
+        <v>679746</v>
       </c>
       <c r="R21" t="n">
-        <v>7321796</v>
+        <v>7322048</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2870,7 +2881,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2880,7 +2891,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,27 +2906,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637870</t>
+          <t>https://artportalen.se/Sighting/135619971</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135619972</v>
+        <v>135619976</v>
       </c>
       <c r="B22" t="n">
-        <v>78447</v>
+        <v>78846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,21 +2934,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2947,13 +2958,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>679746</v>
+        <v>679673</v>
       </c>
       <c r="R22" t="n">
-        <v>7322048</v>
+        <v>7322179</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2982,7 +2993,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2992,7 +3003,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3018,16 +3029,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619972</t>
+          <t>https://artportalen.se/Sighting/135619976</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135619975</v>
+        <v>135637877</v>
       </c>
       <c r="B23" t="n">
-        <v>78447</v>
+        <v>78846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3035,37 +3046,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679673</v>
+        <v>679736</v>
       </c>
       <c r="R23" t="n">
-        <v>7322179</v>
+        <v>7321943</v>
       </c>
       <c r="S23" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3094,7 +3105,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3104,7 +3115,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,27 +3130,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619975</t>
+          <t>https://artportalen.se/Sighting/135637877</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135619953</v>
+        <v>136146425</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>78847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,42 +3158,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679642</v>
+        <v>679405</v>
       </c>
       <c r="R24" t="n">
-        <v>7321835</v>
+        <v>7321902</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3206,27 +3212,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,27 +3242,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619953</t>
+          <t>https://artportalen.se/Sighting/136146425</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135619957</v>
+        <v>136146439</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>78847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3269,45 +3270,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679790</v>
+        <v>679708</v>
       </c>
       <c r="R25" t="n">
-        <v>7321957</v>
+        <v>7322073</v>
       </c>
       <c r="S25" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3331,34 +3324,29 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3366,27 +3354,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619957</t>
+          <t>https://artportalen.se/Sighting/136146439</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135619963</v>
+        <v>135619952</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>80062</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3394,45 +3382,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679845</v>
+        <v>679574</v>
       </c>
       <c r="R26" t="n">
-        <v>7322112</v>
+        <v>7321815</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3461,7 +3441,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3471,19 +3451,14 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3502,16 +3477,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619963</t>
+          <t>https://artportalen.se/Sighting/135619952</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135619964</v>
+        <v>135619958</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>80062</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,42 +3494,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679863</v>
+        <v>679814</v>
       </c>
       <c r="R27" t="n">
-        <v>7322052</v>
+        <v>7321960</v>
       </c>
       <c r="S27" t="n">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3583,7 +3553,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3593,12 +3563,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,16 +3589,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619964</t>
+          <t>https://artportalen.se/Sighting/135619958</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135619966</v>
+        <v>135619969</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>80062</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3641,45 +3606,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679785</v>
+        <v>679744</v>
       </c>
       <c r="R28" t="n">
-        <v>7322100</v>
+        <v>7322052</v>
       </c>
       <c r="S28" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3708,7 +3665,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3718,19 +3675,14 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3749,16 +3701,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619966</t>
+          <t>https://artportalen.se/Sighting/135619969</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135619982</v>
+        <v>135619981</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>80062</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,45 +3718,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679625</v>
+        <v>679630</v>
       </c>
       <c r="R29" t="n">
-        <v>7322249</v>
+        <v>7322240</v>
       </c>
       <c r="S29" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3833,7 +3777,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3843,19 +3787,14 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -3874,16 +3813,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619982</t>
+          <t>https://artportalen.se/Sighting/135619981</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135637884</v>
+        <v>135637870</v>
       </c>
       <c r="B30" t="n">
-        <v>57982</v>
+        <v>80062</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3891,21 +3830,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3915,13 +3854,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679841</v>
+        <v>679550</v>
       </c>
       <c r="R30" t="n">
-        <v>7322162</v>
+        <v>7321796</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3950,7 +3889,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3960,12 +3899,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3991,16 +3925,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637884</t>
+          <t>https://artportalen.se/Sighting/135637870</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135637885</v>
+        <v>136146420</v>
       </c>
       <c r="B31" t="n">
-        <v>57982</v>
+        <v>80063</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4008,21 +3942,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4032,13 +3966,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679690</v>
+        <v>679343</v>
       </c>
       <c r="R31" t="n">
-        <v>7322205</v>
+        <v>7321988</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4062,27 +3996,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4108,16 +4037,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637885</t>
+          <t>https://artportalen.se/Sighting/136146420</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135637886</v>
+        <v>136146430</v>
       </c>
       <c r="B32" t="n">
-        <v>57982</v>
+        <v>80063</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4125,21 +4054,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4149,13 +4078,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679785</v>
+        <v>679424</v>
       </c>
       <c r="R32" t="n">
-        <v>7322109</v>
+        <v>7321817</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4179,34 +4108,29 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
@@ -4225,16 +4149,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637886</t>
+          <t>https://artportalen.se/Sighting/136146430</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135637888</v>
+        <v>136146436</v>
       </c>
       <c r="B33" t="n">
-        <v>57982</v>
+        <v>80063</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4242,21 +4166,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4266,13 +4190,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679854</v>
+        <v>679403</v>
       </c>
       <c r="R33" t="n">
-        <v>7322119</v>
+        <v>7322044</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4296,34 +4220,29 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>äldre bohål i en björk direkt under en (eld)ticka. På grund av den mycket runda formen och den lilla diametern (cirka 4 cm) skulle det mycket väl kunna vara gjort av en tretåig hackspett.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4342,16 +4261,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637888</t>
+          <t>https://artportalen.se/Sighting/136146436</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135637890</v>
+        <v>135619972</v>
       </c>
       <c r="B34" t="n">
-        <v>57982</v>
+        <v>78447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,42 +4278,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679438</v>
+        <v>679746</v>
       </c>
       <c r="R34" t="n">
-        <v>7322215</v>
+        <v>7322048</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4426,7 +4337,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4436,19 +4347,14 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>fodersök på gran</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4456,27 +4362,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637890</t>
+          <t>https://artportalen.se/Sighting/135619972</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135637892</v>
+        <v>135619975</v>
       </c>
       <c r="B35" t="n">
-        <v>57982</v>
+        <v>78447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,37 +4390,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679377</v>
+        <v>679673</v>
       </c>
       <c r="R35" t="n">
-        <v>7321710</v>
+        <v>7322179</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4543,7 +4449,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4553,12 +4459,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4573,24 +4474,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637892</t>
+          <t>https://artportalen.se/Sighting/135619975</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135649674</v>
+        <v>135619953</v>
       </c>
       <c r="B36" t="n">
         <v>57982</v>
@@ -4618,28 +4519,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679561</v>
+        <v>679642</v>
       </c>
       <c r="R36" t="n">
-        <v>7322053</v>
+        <v>7321835</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4663,27 +4561,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ljudinspelningar med både läten och trumningar finns</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4698,24 +4596,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135649674</t>
+          <t>https://artportalen.se/Sighting/135619953</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135649680</v>
+        <v>135619957</v>
       </c>
       <c r="B37" t="n">
         <v>57982</v>
@@ -4743,36 +4641,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679602</v>
+        <v>679790</v>
       </c>
       <c r="R37" t="n">
-        <v>7322064</v>
+        <v>7321957</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4801,7 +4691,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4811,14 +4701,19 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4826,24 +4721,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135649680</t>
+          <t>https://artportalen.se/Sighting/135619957</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135952178</v>
+        <v>135619963</v>
       </c>
       <c r="B38" t="n">
         <v>57982</v>
@@ -4872,19 +4767,27 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Soubdicke3, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679843</v>
+        <v>679845</v>
       </c>
       <c r="R38" t="n">
-        <v>7322138</v>
+        <v>7322112</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4908,34 +4811,34 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG38" t="b">
         <v>0</v>
@@ -4943,24 +4846,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135952178</t>
+          <t>https://artportalen.se/Sighting/135619963</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135952414</v>
+        <v>135619964</v>
       </c>
       <c r="B39" t="n">
         <v>57982</v>
@@ -4989,19 +4892,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679677</v>
+        <v>679863</v>
       </c>
       <c r="R39" t="n">
-        <v>7322293</v>
+        <v>7322052</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5025,34 +4933,34 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska spår fodersök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="b">
         <v>0</v>
@@ -5060,24 +4968,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135952414</t>
+          <t>https://artportalen.se/Sighting/135619964</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135952417</v>
+        <v>135619966</v>
       </c>
       <c r="B40" t="n">
         <v>57982</v>
@@ -5110,23 +5018,23 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679684</v>
+        <v>679785</v>
       </c>
       <c r="R40" t="n">
-        <v>7321810</v>
+        <v>7322100</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5150,34 +5058,34 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack tall</t>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -5185,24 +5093,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135952417</t>
+          <t>https://artportalen.se/Sighting/135619966</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135952418</v>
+        <v>135619982</v>
       </c>
       <c r="B41" t="n">
         <v>57982</v>
@@ -5231,19 +5139,27 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Soubdicke1, Pi lm</t>
+          <t>Norrstrand, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679649</v>
+        <v>679625</v>
       </c>
       <c r="R41" t="n">
-        <v>7321825</v>
+        <v>7322249</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5267,34 +5183,34 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -5302,27 +5218,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135952418</t>
+          <t>https://artportalen.se/Sighting/135619982</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135619973</v>
+        <v>135637884</v>
       </c>
       <c r="B42" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5330,37 +5246,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679752</v>
+        <v>679841</v>
       </c>
       <c r="R42" t="n">
-        <v>7322097</v>
+        <v>7322162</v>
       </c>
       <c r="S42" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5389,7 +5305,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5399,7 +5315,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5414,27 +5335,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619973</t>
+          <t>https://artportalen.se/Sighting/135637884</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135650299</v>
+        <v>135637885</v>
       </c>
       <c r="B43" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5442,45 +5363,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679561</v>
+        <v>679690</v>
       </c>
       <c r="R43" t="n">
-        <v>7322053</v>
+        <v>7322205</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5509,22 +5422,22 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ljudinspelning finns</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5550,16 +5463,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135650299</t>
+          <t>https://artportalen.se/Sighting/135637885</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135619960</v>
+        <v>135637886</v>
       </c>
       <c r="B44" t="n">
-        <v>58086</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5567,16 +5480,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5585,24 +5498,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679846</v>
+        <v>679785</v>
       </c>
       <c r="R44" t="n">
-        <v>7321962</v>
+        <v>7322109</v>
       </c>
       <c r="S44" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5631,7 +5539,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5641,14 +5549,19 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5656,27 +5569,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619960</t>
+          <t>https://artportalen.se/Sighting/135637886</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135637879</v>
+        <v>135637888</v>
       </c>
       <c r="B45" t="n">
-        <v>58086</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5684,16 +5597,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5701,28 +5614,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679797</v>
+        <v>679854</v>
       </c>
       <c r="R45" t="n">
-        <v>7321975</v>
+        <v>7322119</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5751,7 +5656,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5761,14 +5666,19 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>äldre bohål i en björk direkt under en (eld)ticka. På grund av den mycket runda formen och den lilla diametern (cirka 4 cm) skulle det mycket väl kunna vara gjort av en tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG45" t="b">
         <v>0</v>
@@ -5787,16 +5697,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135637879</t>
+          <t>https://artportalen.se/Sighting/135637888</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135619970</v>
+        <v>135637890</v>
       </c>
       <c r="B46" t="n">
-        <v>80033</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5804,37 +5714,45 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679752</v>
+        <v>679438</v>
       </c>
       <c r="R46" t="n">
-        <v>7322054</v>
+        <v>7322215</v>
       </c>
       <c r="S46" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5863,7 +5781,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5873,14 +5791,19 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>fodersök på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5888,27 +5811,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619970</t>
+          <t>https://artportalen.se/Sighting/135637890</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135619974</v>
+        <v>135637892</v>
       </c>
       <c r="B47" t="n">
-        <v>80033</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5916,34 +5839,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679682</v>
+        <v>679377</v>
       </c>
       <c r="R47" t="n">
-        <v>7322160</v>
+        <v>7321710</v>
       </c>
       <c r="S47" t="n">
         <v>7</v>
@@ -5975,7 +5898,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5985,7 +5908,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6000,27 +5928,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619974</t>
+          <t>https://artportalen.se/Sighting/135637892</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135619961</v>
+        <v>135649674</v>
       </c>
       <c r="B48" t="n">
-        <v>79466</v>
+        <v>57982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6028,37 +5956,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679862</v>
+        <v>679561</v>
       </c>
       <c r="R48" t="n">
-        <v>7321960</v>
+        <v>7322053</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6082,22 +6018,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ljudinspelningar med både läten och trumningar finns</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6112,60 +6053,81 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619961</t>
+          <t>https://artportalen.se/Sighting/135649674</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135619954</v>
+        <v>135649680</v>
       </c>
       <c r="B49" t="n">
-        <v>80337</v>
+        <v>57982</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>266179</v>
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Vain.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke1, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679703</v>
+        <v>679602</v>
       </c>
       <c r="R49" t="n">
-        <v>7321883</v>
+        <v>7322064</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6194,7 +6156,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6204,7 +6166,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6219,60 +6181,65 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135619954</t>
+          <t>https://artportalen.se/Sighting/135649680</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135619980</v>
+        <v>135952178</v>
       </c>
       <c r="B50" t="n">
-        <v>80337</v>
+        <v>57982</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>266179</v>
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Norrstrand, Pi lm</t>
+          <t>Soubdicke3, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679628</v>
+        <v>679843</v>
       </c>
       <c r="R50" t="n">
-        <v>7322239</v>
+        <v>7322138</v>
       </c>
       <c r="S50" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6296,22 +6263,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6326,16 +6298,1864 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135952178</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135952414</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>679677</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7322293</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska spår fodersök</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135952414</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135952417</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>679684</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7321810</v>
+      </c>
+      <c r="S52" t="n">
+        <v>6</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135952417</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135952418</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>679649</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7321825</v>
+      </c>
+      <c r="S53" t="n">
+        <v>7</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135952418</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136146441</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>679790</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7321960</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>fodersök på gran</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136146441</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135619973</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>679752</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7322097</v>
+      </c>
+      <c r="S55" t="n">
+        <v>48</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619973</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135650299</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>679561</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7322053</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>ljudinspelning finns</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650299</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135619960</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58086</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>679846</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7321962</v>
+      </c>
+      <c r="S57" t="n">
+        <v>21</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619960</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135637879</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58086</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>679797</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7321975</v>
+      </c>
+      <c r="S58" t="n">
+        <v>8</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135637879</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136146423</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58086</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>679407</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7321920</v>
+      </c>
+      <c r="S59" t="n">
+        <v>7</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136146423</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135619970</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>679752</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7322054</v>
+      </c>
+      <c r="S60" t="n">
+        <v>14</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619970</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135619974</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>679682</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7322160</v>
+      </c>
+      <c r="S61" t="n">
+        <v>7</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619974</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136146427</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80034</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>679398</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7321801</v>
+      </c>
+      <c r="S62" t="n">
+        <v>7</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136146427</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135619961</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79466</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>679862</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7321960</v>
+      </c>
+      <c r="S63" t="n">
+        <v>11</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619961</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136146431</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Soubdicke1, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>679427</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7321815</v>
+      </c>
+      <c r="S64" t="n">
+        <v>6</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136146431</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135619954</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80337</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>679703</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7321883</v>
+      </c>
+      <c r="S65" t="n">
+        <v>8</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619954</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135619980</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80337</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Norrstrand, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>679628</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7322239</v>
+      </c>
+      <c r="S66" t="n">
+        <v>33</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Heike Kontermann, Roger Marklund, Dan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135619980</t>
         </is>
@@ -6392,6 +8212,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>135619959</v>
       </c>
       <c r="B5" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135619965</v>
       </c>
       <c r="B6" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>135952415</v>
       </c>
       <c r="B9" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>135619977</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135952413</v>
       </c>
       <c r="B11" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>135637876</v>
       </c>
       <c r="B12" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>135637880</v>
       </c>
       <c r="B13" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135619967</v>
       </c>
       <c r="B16" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135619978</v>
       </c>
       <c r="B17" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>135637882</v>
       </c>
       <c r="B18" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>135619962</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135619971</v>
       </c>
       <c r="B21" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>135619976</v>
       </c>
       <c r="B22" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135637877</v>
       </c>
       <c r="B23" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135619952</v>
       </c>
       <c r="B26" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>135619958</v>
       </c>
       <c r="B27" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>135619969</v>
       </c>
       <c r="B28" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>135619981</v>
       </c>
       <c r="B29" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>135637870</v>
       </c>
       <c r="B30" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>135619972</v>
       </c>
       <c r="B34" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>135619975</v>
       </c>
       <c r="B35" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>135619970</v>
       </c>
       <c r="B60" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>135619974</v>
       </c>
       <c r="B61" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>135619961</v>
       </c>
       <c r="B63" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>135619954</v>
       </c>
       <c r="B65" t="n">
-        <v>80337</v>
+        <v>80338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>135619980</v>
       </c>
       <c r="B66" t="n">
-        <v>80337</v>
+        <v>80338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>135619977</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135952413</v>
       </c>
       <c r="B11" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>135637876</v>
       </c>
       <c r="B12" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>135637880</v>
       </c>
       <c r="B13" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135619967</v>
       </c>
       <c r="B16" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135619978</v>
       </c>
       <c r="B17" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>135637882</v>
       </c>
       <c r="B18" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135619959</v>
       </c>
       <c r="B5" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135619965</v>
       </c>
       <c r="B6" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136146432</v>
       </c>
       <c r="B7" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136146442</v>
       </c>
       <c r="B8" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>135952415</v>
       </c>
       <c r="B9" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>135619977</v>
       </c>
       <c r="B10" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135952413</v>
       </c>
       <c r="B11" t="n">
-        <v>92259</v>
+        <v>92260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>135637876</v>
       </c>
       <c r="B12" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>135637880</v>
       </c>
       <c r="B13" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135619967</v>
       </c>
       <c r="B16" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135619978</v>
       </c>
       <c r="B17" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>135637882</v>
       </c>
       <c r="B18" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>135619962</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135619971</v>
       </c>
       <c r="B21" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>135619976</v>
       </c>
       <c r="B22" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135637877</v>
       </c>
       <c r="B23" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136146425</v>
       </c>
       <c r="B24" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>136146439</v>
       </c>
       <c r="B25" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135619952</v>
       </c>
       <c r="B26" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>135619958</v>
       </c>
       <c r="B27" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>135619969</v>
       </c>
       <c r="B28" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>135619981</v>
       </c>
       <c r="B29" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>135637870</v>
       </c>
       <c r="B30" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136146420</v>
       </c>
       <c r="B31" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>136146430</v>
       </c>
       <c r="B32" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>136146436</v>
       </c>
       <c r="B33" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>135619972</v>
       </c>
       <c r="B34" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>135619975</v>
       </c>
       <c r="B35" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>135619953</v>
       </c>
       <c r="B36" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>135619957</v>
       </c>
       <c r="B37" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>135619963</v>
       </c>
       <c r="B38" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>135619964</v>
       </c>
       <c r="B39" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>135619966</v>
       </c>
       <c r="B40" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>135619982</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>135637884</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>135637885</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>135637886</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>135637888</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135637890</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>135637892</v>
       </c>
       <c r="B47" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>135649674</v>
       </c>
       <c r="B48" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>135649680</v>
       </c>
       <c r="B49" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>135952178</v>
       </c>
       <c r="B50" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>135952414</v>
       </c>
       <c r="B51" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>135952417</v>
       </c>
       <c r="B52" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>135952418</v>
       </c>
       <c r="B53" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>136146441</v>
       </c>
       <c r="B54" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>135619973</v>
       </c>
       <c r="B55" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>135650299</v>
       </c>
       <c r="B56" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>135619960</v>
       </c>
       <c r="B57" t="n">
-        <v>58086</v>
+        <v>58087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>135637879</v>
       </c>
       <c r="B58" t="n">
-        <v>58086</v>
+        <v>58087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136146423</v>
       </c>
       <c r="B59" t="n">
-        <v>58086</v>
+        <v>58087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>135619970</v>
       </c>
       <c r="B60" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>135619974</v>
       </c>
       <c r="B61" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>136146427</v>
       </c>
       <c r="B62" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>135619961</v>
       </c>
       <c r="B63" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>136146431</v>
       </c>
       <c r="B64" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>135619954</v>
       </c>
       <c r="B65" t="n">
-        <v>80338</v>
+        <v>80339</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>135619980</v>
       </c>
       <c r="B66" t="n">
-        <v>80338</v>
+        <v>80339</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136146432</v>
       </c>
       <c r="B7" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136146442</v>
       </c>
       <c r="B8" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>135952415</v>
       </c>
       <c r="B9" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135952413</v>
       </c>
       <c r="B11" t="n">
-        <v>92260</v>
+        <v>92266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>135637876</v>
       </c>
       <c r="B12" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>135637880</v>
       </c>
       <c r="B13" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>135637882</v>
       </c>
       <c r="B18" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135637877</v>
       </c>
       <c r="B23" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136146425</v>
       </c>
       <c r="B24" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>136146439</v>
       </c>
       <c r="B25" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>135637870</v>
       </c>
       <c r="B30" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136146420</v>
       </c>
       <c r="B31" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>136146430</v>
       </c>
       <c r="B32" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>136146436</v>
       </c>
       <c r="B33" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>135637884</v>
       </c>
       <c r="B42" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>135637885</v>
       </c>
       <c r="B43" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>135637886</v>
       </c>
       <c r="B44" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>135637888</v>
       </c>
       <c r="B45" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135637890</v>
       </c>
       <c r="B46" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>135637892</v>
       </c>
       <c r="B47" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>135649674</v>
       </c>
       <c r="B48" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>135649680</v>
       </c>
       <c r="B49" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>135952178</v>
       </c>
       <c r="B50" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>135952414</v>
       </c>
       <c r="B51" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>135952417</v>
       </c>
       <c r="B52" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>135952418</v>
       </c>
       <c r="B53" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>136146441</v>
       </c>
       <c r="B54" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>135650299</v>
       </c>
       <c r="B56" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>135637879</v>
       </c>
       <c r="B58" t="n">
-        <v>58087</v>
+        <v>58091</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136146423</v>
       </c>
       <c r="B59" t="n">
-        <v>58087</v>
+        <v>58091</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>136146427</v>
       </c>
       <c r="B62" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>136146431</v>
       </c>
       <c r="B64" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136146432</v>
       </c>
       <c r="B7" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136146442</v>
       </c>
       <c r="B8" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>135952415</v>
       </c>
       <c r="B9" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135952413</v>
       </c>
       <c r="B11" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136146425</v>
       </c>
       <c r="B24" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>136146439</v>
       </c>
       <c r="B25" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136146420</v>
       </c>
       <c r="B31" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>136146430</v>
       </c>
       <c r="B32" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>136146436</v>
       </c>
       <c r="B33" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135637890</v>
       </c>
       <c r="B46" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>135649674</v>
       </c>
       <c r="B48" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>135952178</v>
       </c>
       <c r="B50" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>135952414</v>
       </c>
       <c r="B51" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>135952417</v>
       </c>
       <c r="B52" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>135952418</v>
       </c>
       <c r="B53" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>136146441</v>
       </c>
       <c r="B54" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>135650299</v>
       </c>
       <c r="B56" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136146423</v>
       </c>
       <c r="B59" t="n">
-        <v>58091</v>
+        <v>58092</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>136146427</v>
       </c>
       <c r="B62" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>136146431</v>
       </c>
       <c r="B64" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136146432</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136146442</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>135952415</v>
       </c>
       <c r="B9" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135952413</v>
       </c>
       <c r="B11" t="n">
-        <v>92267</v>
+        <v>92273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136146425</v>
       </c>
       <c r="B24" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>136146439</v>
       </c>
       <c r="B25" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136146420</v>
       </c>
       <c r="B31" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>136146430</v>
       </c>
       <c r="B32" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>136146436</v>
       </c>
       <c r="B33" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>136146427</v>
       </c>
       <c r="B62" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>136146431</v>
       </c>
       <c r="B64" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136146432</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136146442</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>135952415</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135952413</v>
       </c>
       <c r="B11" t="n">
-        <v>92273</v>
+        <v>92280</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136146425</v>
       </c>
       <c r="B24" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>136146439</v>
       </c>
       <c r="B25" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136146420</v>
       </c>
       <c r="B31" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>136146430</v>
       </c>
       <c r="B32" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>136146436</v>
       </c>
       <c r="B33" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>135637890</v>
       </c>
       <c r="B46" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>135649674</v>
       </c>
       <c r="B48" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>135952178</v>
       </c>
       <c r="B50" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>135952414</v>
       </c>
       <c r="B51" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>135952417</v>
       </c>
       <c r="B52" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>135952418</v>
       </c>
       <c r="B53" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>136146441</v>
       </c>
       <c r="B54" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>135650299</v>
       </c>
       <c r="B56" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136146423</v>
       </c>
       <c r="B59" t="n">
-        <v>58092</v>
+        <v>58097</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>136146427</v>
       </c>
       <c r="B62" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>136146431</v>
       </c>
       <c r="B64" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135952413</v>
       </c>
       <c r="B11" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136146432</v>
       </c>
       <c r="B7" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136146442</v>
       </c>
       <c r="B8" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>135952415</v>
       </c>
       <c r="B9" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135952413</v>
       </c>
       <c r="B11" t="n">
-        <v>92281</v>
+        <v>92294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136146425</v>
       </c>
       <c r="B24" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>136146439</v>
       </c>
       <c r="B25" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136146420</v>
       </c>
       <c r="B31" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>136146430</v>
       </c>
       <c r="B32" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>136146436</v>
       </c>
       <c r="B33" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>135952178</v>
       </c>
       <c r="B50" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>135952414</v>
       </c>
       <c r="B51" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>135952417</v>
       </c>
       <c r="B52" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>135952418</v>
       </c>
       <c r="B53" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>136146441</v>
       </c>
       <c r="B54" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136146423</v>
       </c>
       <c r="B59" t="n">
-        <v>58097</v>
+        <v>58110</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>136146427</v>
       </c>
       <c r="B62" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>136146431</v>
       </c>
       <c r="B64" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136146432</v>
       </c>
       <c r="B7" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136146442</v>
       </c>
       <c r="B8" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>135952415</v>
       </c>
       <c r="B9" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135952413</v>
       </c>
       <c r="B11" t="n">
-        <v>92294</v>
+        <v>92295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136146425</v>
       </c>
       <c r="B24" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>136146439</v>
       </c>
       <c r="B25" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136146420</v>
       </c>
       <c r="B31" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>136146430</v>
       </c>
       <c r="B32" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>136146436</v>
       </c>
       <c r="B33" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>136146427</v>
       </c>
       <c r="B62" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>136146431</v>
       </c>
       <c r="B64" t="n">
-        <v>79496</v>
+        <v>79497</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
